--- a/output/pdf_financials_xlsx/ELD.xlsx
+++ b/output/pdf_financials_xlsx/ELD.xlsx
@@ -1375,7 +1375,7 @@
         <v>-649.615</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>106.544</v>
+        <v>-106.544</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-1645.142</v>
@@ -1683,7 +1683,7 @@
         <v>-649.615</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>106.544</v>
+        <v>-106.544</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-1645.142</v>
@@ -1867,7 +1867,7 @@
         <v>-649.615</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>106.544</v>
+        <v>-106.544</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-1645.142</v>
@@ -2153,7 +2153,7 @@
         <v>-649.615</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>106.544</v>
+        <v>-106.544</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-1645.142</v>
@@ -2277,7 +2277,7 @@
         <v>-500.547</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>283.771</v>
+        <v>70.68300000000001</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-1466.164</v>
@@ -2429,7 +2429,7 @@
         <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
@@ -6635,7 +6635,7 @@
         <v>-649.615</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>106.544</v>
+        <v>-106.544</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>-1645.142</v>
@@ -59013,7 +59013,7 @@
         <v>-649.615</v>
       </c>
       <c r="K514" s="5" t="n">
-        <v>106.544</v>
+        <v>-106.544</v>
       </c>
       <c r="L514" s="5" t="n">
         <v>-1645.142</v>
@@ -86394,7 +86394,7 @@
         </is>
       </c>
       <c r="K791" s="5" t="n">
-        <v>106.544</v>
+        <v>-106.544</v>
       </c>
       <c r="L791" s="5" t="n">
         <v>-1645.142</v>
@@ -87002,7 +87002,7 @@
         <v>-649.615</v>
       </c>
       <c r="K797" s="5" t="n">
-        <v>106.544</v>
+        <v>-106.544</v>
       </c>
       <c r="L797" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ELD.xlsx
+++ b/output/pdf_financials_xlsx/ELD.xlsx
@@ -7893,13 +7893,13 @@
         <v>0</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>0</v>
+        <v>14.552</v>
       </c>
       <c r="O120" s="3" t="n">
-        <v>0</v>
+        <v>14.101</v>
       </c>
       <c r="P120" s="3" t="n">
-        <v>0</v>
+        <v>168.664</v>
       </c>
       <c r="Q120" s="3" t="n">
         <v>0</v>
@@ -8205,28 +8205,28 @@
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="C126" s="3" t="n">
-        <v>0</v>
+        <v>-0.149</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>-26.357</v>
+        <v>-7.58</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>0</v>
+        <v>-8.095000000000001</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>0</v>
+        <v>-9.398999999999999</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>0</v>
+        <v>-13.281</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>0</v>
+        <v>-12.466</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>0</v>
+        <v>-10.929</v>
       </c>
       <c r="J126" s="3" t="n">
         <v>0</v>
@@ -48938,7 +48938,11 @@
           <t>Issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -60056,7 +60060,11 @@
           <t>Dividend paid to non-controlling interests</t>
         </is>
       </c>
-      <c r="D525" t="inlineStr"/>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E525" t="inlineStr">
         <is>
           <t>-</t>
@@ -60745,7 +60753,11 @@
           <t>Dividend paid to non-controlling interests</t>
         </is>
       </c>
-      <c r="D532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E532" t="inlineStr">
         <is>
           <t>-</t>
@@ -66410,7 +66422,11 @@
           <t>Dividend paid to non-controlling interest</t>
         </is>
       </c>
-      <c r="D589" t="inlineStr"/>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E589" s="5" t="n">
         <v>-0.3</v>
       </c>

--- a/output/pdf_financials_xlsx/ELD.xlsx
+++ b/output/pdf_financials_xlsx/ELD.xlsx
@@ -593,45 +593,29 @@
       <c r="J4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K4" s="3" t="n">
+        <v>391.406</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>459.016</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>617.823</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>940.914</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>871.984</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>1008.501</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>1322.581</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>1818.856</v>
       </c>
     </row>
     <row r="5">
@@ -687,15 +671,11 @@
       <c r="P5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -733,45 +713,29 @@
       <c r="J6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K6" s="3" t="n">
+        <v>391.406</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>459.016</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>617.823</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>940.914</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>871.984</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>1008.501</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>1322.581</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>1818.856</v>
       </c>
     </row>
     <row r="7">
@@ -827,15 +791,11 @@
       <c r="P7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -891,15 +851,11 @@
       <c r="P8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -955,15 +911,11 @@
       <c r="P9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1019,15 +971,11 @@
       <c r="P10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1074,30 +1022,20 @@
       <c r="M11" s="3" t="n">
         <v>146.837</v>
       </c>
-      <c r="N11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N11" s="3" t="n">
+        <v>217.89</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>41.679</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>182.009</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>419.393</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>727.399</v>
       </c>
     </row>
     <row r="12">
@@ -1153,15 +1091,11 @@
       <c r="P12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1277,15 +1211,11 @@
       <c r="P14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1692,7 +1622,7 @@
         <v>-346.876</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-21.388</v>
+        <v>-18.591</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-379.631</v>
@@ -1752,7 +1682,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>-2.797</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>0</v>
@@ -1761,23 +1691,19 @@
         <v>0</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>0</v>
+        <v>-156.91</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>0</v>
+        <v>-304.648</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2361,35 +2287,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K30" s="3" t="n">
+        <v>17.91617910813835</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>-78.51512801296687</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>43.14730918078479</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>21.60930754564179</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>-14.38604378061983</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>41.65042969714457</v>
       </c>
       <c r="Q30" s="1" t="inlineStr">
         <is>
@@ -2513,35 +2427,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K32" s="3" t="n">
+        <v>-5.464402691834055</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>-82.70539589033933</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>11.92655501656623</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>-14.4227846540704</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>-48.9519303106479</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>10.05284080035617</v>
       </c>
       <c r="Q32" s="1" t="inlineStr">
         <is>
@@ -2759,25 +2661,25 @@
         <v>0</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0</v>
+        <v>7.037</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0</v>
+        <v>53.147</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>21.51</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>19.771</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0</v>
+        <v>16.137</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0</v>
+        <v>11.053</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>0</v>
+        <v>7.746</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>0</v>
@@ -2999,25 +2901,25 @@
         <v>0</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0</v>
+        <v>7.037</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>53.147</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>21.51</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>19.771</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0</v>
+        <v>16.137</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0</v>
+        <v>11.053</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>7.746</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>0</v>
@@ -3419,25 +3321,25 @@
         <v>76.434</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>97.699</v>
+        <v>90.66200000000001</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>112.565</v>
+        <v>59.418</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>124.195</v>
+        <v>102.685</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>121.057</v>
+        <v>101.286</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>90.098</v>
+        <v>73.961</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>59.847</v>
+        <v>48.794</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>84.16200000000001</v>
+        <v>76.416</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>87.929</v>
@@ -4475,25 +4377,25 @@
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>67.056</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>101.505</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>106.098</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>83.566</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>97.345</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>43.712</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>60.081</v>
       </c>
       <c r="L64" s="3" t="n">
         <v>0</v>
@@ -4655,46 +4557,46 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>61.055</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>103.455</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>98.866</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>94.916</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>133.617</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>46.75</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>50.247</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>98.73</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>58.792</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>105.141</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>112.675</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>127.816</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>179.012</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>287.035</v>
       </c>
     </row>
     <row r="68">
@@ -7063,19 +6965,19 @@
         <v>15.256</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0</v>
+        <v>-9.784000000000001</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0</v>
+        <v>-28.314</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>0</v>
+        <v>-28.282</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0</v>
+        <v>20.554</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>0</v>
+        <v>-9.487</v>
       </c>
     </row>
     <row r="107">
@@ -7118,22 +7020,22 @@
         <v>6.989</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>10.396</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>7.945</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>10.744</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>10.195</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0</v>
+        <v>11.872</v>
       </c>
       <c r="R107" s="3" t="n">
-        <v>0</v>
+        <v>20.224</v>
       </c>
     </row>
     <row r="108">
@@ -7497,10 +7399,10 @@
         <v>0</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>-11.983</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0</v>
+        <v>-1.823</v>
       </c>
       <c r="F114" s="3" t="n">
         <v>0</v>
@@ -7509,13 +7411,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>-3.313</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>0</v>
+        <v>-16.312</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>0</v>
+        <v>-2.526</v>
       </c>
       <c r="K114" s="3" t="n">
         <v>0</v>
@@ -7555,25 +7457,25 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>15.611</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>8.154</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>2.025</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>1.521</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>3.665</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -8863,7 +8765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U853"/>
+  <dimension ref="A1:U894"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11144,7 +11046,11 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -42273,7 +42179,11 @@
           <t>Share-based payments expense 22</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
@@ -43035,7 +42945,11 @@
           <t>Changes in non-cash operating working capital 23</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -48451,7 +48365,11 @@
           <t>Share-based payments expense 21</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
@@ -48548,7 +48466,11 @@
           <t>Changes in non-cash operating working capital 22</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E407" t="inlineStr">
         <is>
           <t>-</t>
@@ -53282,7 +53204,11 @@
           <t>Share based payments expense</t>
         </is>
       </c>
-      <c r="D455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E455" t="inlineStr">
         <is>
           <t>-</t>
@@ -54157,7 +54083,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr"/>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E464" t="inlineStr">
         <is>
           <t>-</t>
@@ -55511,7 +55441,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E478" t="inlineStr">
         <is>
           <t>-</t>
@@ -57449,7 +57383,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E498" t="inlineStr">
         <is>
           <t>-</t>
@@ -58219,7 +58157,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D506" t="inlineStr"/>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E506" t="inlineStr">
         <is>
           <t>-</t>
@@ -58312,7 +58254,11 @@
           <t>Proceeds from the sale of marketable securities</t>
         </is>
       </c>
-      <c r="D507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E507" t="inlineStr">
         <is>
           <t>-</t>
@@ -60254,7 +60200,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D527" t="inlineStr"/>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E527" t="inlineStr">
         <is>
           <t>-</t>
@@ -70626,7 +70576,11 @@
           <t>Metal sales 30 $</t>
         </is>
       </c>
-      <c r="D631" t="inlineStr"/>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E631" t="inlineStr">
         <is>
           <t>-</t>
@@ -70998,7 +70952,11 @@
           <t>Earnings from mine operations</t>
         </is>
       </c>
-      <c r="D635" t="inlineStr"/>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E635" t="inlineStr">
         <is>
           <t>-</t>
@@ -71730,7 +71688,11 @@
           <t>Earnings from operations</t>
         </is>
       </c>
-      <c r="D643" t="inlineStr"/>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E643" t="inlineStr">
         <is>
           <t>-</t>
@@ -76258,7 +76220,11 @@
           <t>Metal sales 29 $</t>
         </is>
       </c>
-      <c r="D689" t="inlineStr"/>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E689" t="inlineStr">
         <is>
           <t>-</t>
@@ -78240,7 +78206,11 @@
           <t>Metal sales 28 $</t>
         </is>
       </c>
-      <c r="D709" t="inlineStr"/>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E709" t="inlineStr">
         <is>
           <t>-</t>
@@ -79240,7 +79210,11 @@
           <t>Loss from discontinued operations</t>
         </is>
       </c>
-      <c r="D719" t="inlineStr"/>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E719" t="inlineStr">
         <is>
           <t>-</t>
@@ -79438,7 +79412,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D721" t="inlineStr"/>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E721" t="inlineStr">
         <is>
           <t>-</t>
@@ -84388,7 +84366,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D771" t="inlineStr"/>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E771" t="inlineStr">
         <is>
           <t>-</t>
@@ -84487,7 +84469,11 @@
           <t>Loss from discontinued operations</t>
         </is>
       </c>
-      <c r="D772" t="inlineStr"/>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E772" t="inlineStr">
         <is>
           <t>-</t>
@@ -92676,6 +92662,4179 @@
         </is>
       </c>
       <c r="U853" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>is included below</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>Gold ounces sold 360,227</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr"/>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G854" s="5" t="n">
+        <v>316.918</v>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>is included below</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>Operating costs $132,464</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr"/>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G855" s="5" t="n">
+        <v>92.004</v>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>is included below</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>Royalty expense and production taxes (10,025)</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr"/>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G856" s="5" t="n">
+        <v>-10.117</v>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>is included below</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>Effects of inventory adjustments (2,342)</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr"/>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G857" s="5" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>is included below</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>Fair value of stock option grants (1,830)</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr"/>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G858" s="5" t="n">
+        <v>-1.526</v>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>is included below</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>Sino Gold inventory fair value adjustment (6,957)</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr"/>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>is included below</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>Expense of certain development costs -</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr"/>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>is included below</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>Cash operating cost $111,310</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr"/>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G861" s="5" t="n">
+        <v>80.986</v>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>is included below</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>Cash operating cost per ounce $ 309 $</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr"/>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G862" s="5" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>SEDAR at www.sedar.com.</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>SEDAR at www.sedar.com.</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr"/>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G863" s="5" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>Gold sales 358,467</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr"/>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G864" s="5" t="n">
+        <v>277.723</v>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>Interest and other income 2,262</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G865" s="5" t="n">
+        <v>10.508</v>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>Operating costs 132,464</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr"/>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G866" s="5" t="n">
+        <v>92.004</v>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>Depletion, depreciation and amortization 38,658</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G867" s="5" t="n">
+        <v>25.995</v>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>General and administrative 32,530</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G868" s="5" t="n">
+        <v>38.299</v>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>Exploration 11,970</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr"/>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G869" s="5" t="n">
+        <v>12.316</v>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>Mine standby costs 2,580</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr"/>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G870" s="5" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>Asset retirement obligation costs (note 14) 291</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr"/>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G871" s="5" t="n">
+        <v>3.108</v>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Foreign exchange (gain) loss (2,966)</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr"/>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G872" s="5" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>Gain on disposal of assets (854)</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr"/>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G873" s="5" t="n">
+        <v>-70.774</v>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>Gain on marketable securities (1,689)</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr"/>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G874" s="5" t="n">
+        <v>-2.475</v>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>Interest and financing costs 824</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr"/>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G875" s="5" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>Loss on derivative contract (note 9) -</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr"/>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G876" s="5" t="n">
+        <v>2.956</v>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>Income before income taxes and non-controlling interests 146,921</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr"/>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G877" s="5" t="n">
+        <v>181.254</v>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>Income tax (expense) recovery (note</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G878" s="5" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>Current (44,862)</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr"/>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G879" s="5" t="n">
+        <v>-25.403</v>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>Future 2,972</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr"/>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G880" s="5" t="n">
+        <v>12.904</v>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>Non-controlling interests (2,627)</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr"/>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G881" s="5" t="n">
+        <v>-5.099</v>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Net income for the year 102,404</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G882" s="5" t="n">
+        <v>163.656</v>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>Deficit, beginning of year (153,520)</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr"/>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G883" s="5" t="n">
+        <v>-317.176</v>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>Deficit, end of year (51,116)</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr"/>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G884" s="5" t="n">
+        <v>-153.52</v>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>Basic 389,384</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G885" s="5" t="n">
+        <v>0.355132</v>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>Diluted 391,707</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G886" s="5" t="n">
+        <v>0.356308</v>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Earnings per share</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>Basic income per share ― US$ 0.26</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr"/>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G887" s="5" t="n">
+        <v>4.6e-07</v>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Earnings per share</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>Diluted income per share ― US$ 0.26</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr"/>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G888" s="5" t="n">
+        <v>4.6e-07</v>
+      </c>
+      <c r="H888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Earnings per share</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>Earnings per share total</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr"/>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G889" s="5" t="n">
+        <v>0.002008</v>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Earnings per share</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>Net earnings for the year ended December 31, 102,404</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr"/>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G890" s="5" t="n">
+        <v>163.656</v>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>Reversal on acquisition of subsidiary (note 4(a)) (122,617)</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr"/>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G891" s="5" t="n">
+        <v>-0.153</v>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>Realized losses (gains) on available-for-sale investments (note 17(d)) 1,717</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr"/>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G892" s="5" t="n">
+        <v>-0.061</v>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I892" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J892" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K892" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L892" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M892" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N892" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O892" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P892" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q892" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R892" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S892" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T892" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U892" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>Other than temporary impairment charges -</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr"/>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G893" s="5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I893" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J893" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L893" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M893" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N893" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O893" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P893" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q893" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R893" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S893" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T893" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U893" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>Comprehensive income for the year ended December 31, 110,602</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr"/>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G894" s="5" t="n">
+        <v>157.471</v>
+      </c>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I894" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J894" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L894" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M894" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N894" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O894" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P894" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q894" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R894" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S894" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T894" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U894" t="inlineStr">
         <is>
           <t>-</t>
         </is>
